--- a/output/pdf_financials_xlsx/FCA.UN.xlsx
+++ b/output/pdf_financials_xlsx/FCA.UN.xlsx
@@ -976,10 +976,8 @@
       <c r="E23" s="3" t="n">
         <v>-3.428678</v>
       </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F23" s="3" t="n">
+        <v>-7.073669</v>
       </c>
     </row>
     <row r="24">
@@ -2692,10 +2690,8 @@
       <c r="E99" s="3" t="n">
         <v>-3.428678</v>
       </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F99" s="3" t="n">
+        <v>-7.073669</v>
       </c>
     </row>
     <row r="100">
@@ -5843,7 +5839,11 @@
           <t>Net Income / (Loss) $</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -8254,7 +8254,11 @@
           <t>Deferred Tax Recovery 15</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -8783,7 +8787,11 @@
           <t>Net Income (Loss) $</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E136" s="5" t="n">
         <v>3.840463</v>
       </c>
@@ -8900,7 +8908,11 @@
           <t>Deferred Tax Expense 15</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E139" s="5" t="n">
         <v>0.545616</v>
       </c>
